--- a/docs/Results/States/state_population_coverage.xlsx
+++ b/docs/Results/States/state_population_coverage.xlsx
@@ -4747,7 +4747,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -6826,7 +6826,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -6994,7 +6994,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -7435,7 +7435,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -8401,7 +8401,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="C409" t="n">
